--- a/1.xlsx
+++ b/1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="2"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="143">
   <si>
     <t>模块</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -504,19 +504,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>核心</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>升级包</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>链球？连枷？(往目标掷出并拉回，来回造成伤害)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>风火轮（连续攻击多次后触发）（旋转挥舞3圈，挥舞时范围变大）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -546,10 +534,6 @@
       </rPr>
       <t>共振</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>近战核心构思1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -672,6 +656,39 @@
   </si>
   <si>
     <t>生成拳头在角色身边，射程近、伤害高、攻速中等（0.6秒/次）; 攻击时拳头伸出→命中→收回，整个动作0.3秒; 命中敌人时附带轻微停顿。初始只有一个拳头, 可以拓展多一个拳头凑成一对, 交替出拳。最多同时拥有2对拳头, 每一对拳头使用一个脚本控制。将拳头视为子弹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>《几何竞技场》开发规划</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> —— 无人机核心</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高攻速远程攻击, 低加成低伤害。初始1个无人机,可拓展到4个。 主打满屏弹幕。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -789,7 +806,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -881,20 +898,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1211,33 +1234,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="32" t="s">
         <v>117</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A2" s="29"/>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
+      <c r="A2" s="32"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A3" s="29"/>
-      <c r="B3" s="29"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
+      <c r="A3" s="32"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
     </row>
     <row r="4" spans="1:7" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="4" t="s">
@@ -1261,7 +1284,7 @@
       <c r="G4" s="5"/>
     </row>
     <row r="5" spans="1:7" s="2" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="30" t="s">
+      <c r="A5" s="33" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="9" t="s">
@@ -1282,7 +1305,7 @@
       <c r="G5" s="7"/>
     </row>
     <row r="6" spans="1:7" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="30"/>
+      <c r="A6" s="33"/>
       <c r="B6" s="3" t="s">
         <v>113</v>
       </c>
@@ -1300,7 +1323,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="29" t="s">
+      <c r="A7" s="32" t="s">
         <v>11</v>
       </c>
       <c r="B7" s="13" t="s">
@@ -1320,7 +1343,7 @@
       </c>
     </row>
     <row r="8" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="29"/>
+      <c r="A8" s="32"/>
       <c r="B8" s="3" t="s">
         <v>93</v>
       </c>
@@ -1338,23 +1361,23 @@
       </c>
     </row>
     <row r="9" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="29"/>
+      <c r="A9" s="32"/>
       <c r="B9" s="24" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E9" s="21"/>
       <c r="F9" s="24" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="29"/>
+      <c r="A10" s="32"/>
       <c r="B10" s="20" t="s">
         <v>97</v>
       </c>
@@ -1372,7 +1395,7 @@
       </c>
     </row>
     <row r="11" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="29" t="s">
+      <c r="A11" s="32" t="s">
         <v>22</v>
       </c>
       <c r="B11" s="13" t="s">
@@ -1390,14 +1413,14 @@
       <c r="F11" s="13"/>
     </row>
     <row r="12" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="29"/>
+      <c r="A12" s="32"/>
       <c r="B12" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F12" s="19"/>
     </row>
     <row r="13" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="29"/>
+      <c r="A13" s="32"/>
       <c r="B13" s="9" t="s">
         <v>5</v>
       </c>
@@ -1416,7 +1439,7 @@
       <c r="G13" s="7"/>
     </row>
     <row r="14" spans="1:7" s="2" customFormat="1" ht="69.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="30" t="s">
+      <c r="A14" s="33" t="s">
         <v>105</v>
       </c>
       <c r="B14" s="6" t="s">
@@ -1437,7 +1460,7 @@
       <c r="G14" s="7"/>
     </row>
     <row r="15" spans="1:7" s="2" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="30"/>
+      <c r="A15" s="33"/>
       <c r="B15" s="9" t="s">
         <v>25</v>
       </c>
@@ -1456,7 +1479,7 @@
       <c r="G15" s="7"/>
     </row>
     <row r="16" spans="1:7" s="2" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="30"/>
+      <c r="A16" s="33"/>
       <c r="B16" s="15" t="s">
         <v>65</v>
       </c>
@@ -1475,7 +1498,7 @@
       <c r="G16" s="7"/>
     </row>
     <row r="17" spans="1:7" s="2" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="30"/>
+      <c r="A17" s="33"/>
       <c r="B17" s="15" t="s">
         <v>83</v>
       </c>
@@ -1494,7 +1517,7 @@
       <c r="G17" s="7"/>
     </row>
     <row r="18" spans="1:7" s="2" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="30"/>
+      <c r="A18" s="33"/>
       <c r="B18" s="15" t="s">
         <v>70</v>
       </c>
@@ -1513,7 +1536,7 @@
       <c r="G18" s="7"/>
     </row>
     <row r="19" spans="1:7" s="2" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="30" t="s">
+      <c r="A19" s="33" t="s">
         <v>104</v>
       </c>
       <c r="B19" s="6" t="s">
@@ -1526,7 +1549,7 @@
       <c r="G19" s="7"/>
     </row>
     <row r="20" spans="1:7" s="2" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="30"/>
+      <c r="A20" s="33"/>
       <c r="B20" s="22" t="s">
         <v>100</v>
       </c>
@@ -1545,7 +1568,7 @@
       <c r="G20" s="7"/>
     </row>
     <row r="21" spans="1:7" s="2" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="30"/>
+      <c r="A21" s="33"/>
       <c r="B21" s="18" t="s">
         <v>94</v>
       </c>
@@ -1564,7 +1587,7 @@
       <c r="G21" s="7"/>
     </row>
     <row r="22" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="30"/>
+      <c r="A22" s="33"/>
       <c r="B22" s="9" t="s">
         <v>20</v>
       </c>
@@ -1583,7 +1606,7 @@
       <c r="G22" s="7"/>
     </row>
     <row r="23" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="30"/>
+      <c r="A23" s="33"/>
       <c r="B23" s="9" t="s">
         <v>29</v>
       </c>
@@ -1602,7 +1625,7 @@
       <c r="G23" s="7"/>
     </row>
     <row r="24" spans="1:7" s="2" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="30"/>
+      <c r="A24" s="33"/>
       <c r="B24" s="9" t="s">
         <v>34</v>
       </c>
@@ -1621,7 +1644,7 @@
       <c r="G24" s="7"/>
     </row>
     <row r="25" spans="1:7" s="2" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="30"/>
+      <c r="A25" s="33"/>
       <c r="B25" s="9" t="s">
         <v>6</v>
       </c>
@@ -1640,7 +1663,7 @@
       <c r="G25" s="7"/>
     </row>
     <row r="26" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="30"/>
+      <c r="A26" s="33"/>
       <c r="B26" s="9" t="s">
         <v>27</v>
       </c>
@@ -1659,7 +1682,7 @@
       <c r="G26" s="7"/>
     </row>
     <row r="27" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="30"/>
+      <c r="A27" s="33"/>
       <c r="B27" s="9" t="s">
         <v>43</v>
       </c>
@@ -1678,7 +1701,7 @@
       <c r="G27" s="7"/>
     </row>
     <row r="28" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="30"/>
+      <c r="A28" s="33"/>
       <c r="B28" s="9" t="s">
         <v>51</v>
       </c>
@@ -1697,7 +1720,7 @@
       <c r="G28" s="7"/>
     </row>
     <row r="29" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="30"/>
+      <c r="A29" s="33"/>
       <c r="B29" s="9" t="s">
         <v>63</v>
       </c>
@@ -1716,7 +1739,7 @@
       <c r="G29" s="7"/>
     </row>
     <row r="30" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="30" t="s">
+      <c r="A30" s="33" t="s">
         <v>47</v>
       </c>
       <c r="B30" s="9" t="s">
@@ -1737,7 +1760,7 @@
       <c r="G30" s="7"/>
     </row>
     <row r="31" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="30"/>
+      <c r="A31" s="33"/>
       <c r="B31" s="9" t="s">
         <v>48</v>
       </c>
@@ -1756,7 +1779,7 @@
       <c r="G31" s="7"/>
     </row>
     <row r="32" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="30"/>
+      <c r="A32" s="33"/>
       <c r="B32" s="15" t="s">
         <v>68</v>
       </c>
@@ -1775,7 +1798,7 @@
       <c r="G32" s="7"/>
     </row>
     <row r="33" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="30"/>
+      <c r="A33" s="33"/>
       <c r="B33" s="15" t="s">
         <v>80</v>
       </c>
@@ -1794,7 +1817,7 @@
       <c r="G33" s="7"/>
     </row>
     <row r="34" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="30"/>
+      <c r="A34" s="33"/>
       <c r="B34" s="9" t="s">
         <v>67</v>
       </c>
@@ -1813,7 +1836,7 @@
       <c r="G34" s="7"/>
     </row>
     <row r="35" spans="1:7" s="2" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="30"/>
+      <c r="A35" s="33"/>
       <c r="B35" s="6" t="s">
         <v>41</v>
       </c>
@@ -2074,33 +2097,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A1" s="29" t="s">
-        <v>140</v>
-      </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
+      <c r="A1" s="32" t="s">
+        <v>136</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A2" s="29"/>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
+      <c r="A2" s="32"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A3" s="29"/>
-      <c r="B3" s="29"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
+      <c r="A3" s="32"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
     </row>
     <row r="4" spans="1:7" ht="18.75" x14ac:dyDescent="0.15">
       <c r="A4" s="4" t="s">
@@ -2124,7 +2147,7 @@
       <c r="G4" s="5"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A5" s="30" t="s">
+      <c r="A5" s="33" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="9"/>
@@ -2135,7 +2158,7 @@
       <c r="G5" s="7"/>
     </row>
     <row r="6" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="30"/>
+      <c r="A6" s="33"/>
       <c r="B6" s="25"/>
       <c r="C6" s="25"/>
       <c r="D6" s="25"/>
@@ -2143,17 +2166,17 @@
       <c r="F6" s="25"/>
     </row>
     <row r="7" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="29" t="s">
+      <c r="A7" s="32" t="s">
         <v>11</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C7" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="D7" s="13" t="s">
         <v>128</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>132</v>
       </c>
       <c r="E7" s="14">
         <v>1</v>
@@ -2161,33 +2184,33 @@
       <c r="F7" s="9"/>
     </row>
     <row r="8" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="29"/>
+      <c r="A8" s="32"/>
       <c r="B8" s="25" t="s">
+        <v>125</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="D8" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="E8" s="21" t="s">
         <v>129</v>
       </c>
-      <c r="C8" s="25" t="s">
+      <c r="F8" s="25" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="32"/>
+      <c r="B9" s="25" t="s">
         <v>131</v>
       </c>
-      <c r="D8" s="25" t="s">
-        <v>130</v>
-      </c>
-      <c r="E8" s="21" t="s">
+      <c r="C9" s="25" t="s">
+        <v>132</v>
+      </c>
+      <c r="D9" s="25" t="s">
         <v>133</v>
-      </c>
-      <c r="F8" s="25" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="29"/>
-      <c r="B9" s="25" t="s">
-        <v>135</v>
-      </c>
-      <c r="C9" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="D9" s="25" t="s">
-        <v>137</v>
       </c>
       <c r="E9" s="21">
         <v>1</v>
@@ -2195,15 +2218,15 @@
       <c r="F9" s="25"/>
     </row>
     <row r="10" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="29"/>
+      <c r="A10" s="32"/>
       <c r="B10" s="25" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D10" s="25" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E10" s="21">
         <v>1</v>
@@ -2211,7 +2234,7 @@
       <c r="F10" s="25"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A11" s="29" t="s">
+      <c r="A11" s="32" t="s">
         <v>22</v>
       </c>
       <c r="B11" s="13"/>
@@ -2221,7 +2244,7 @@
       <c r="F11" s="13"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A12" s="29"/>
+      <c r="A12" s="32"/>
       <c r="B12" s="25"/>
       <c r="C12" s="25"/>
       <c r="D12" s="25"/>
@@ -2229,7 +2252,7 @@
       <c r="F12" s="26"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A13" s="29"/>
+      <c r="A13" s="32"/>
       <c r="B13" s="9"/>
       <c r="C13" s="10"/>
       <c r="D13" s="11"/>
@@ -2238,7 +2261,7 @@
       <c r="G13" s="7"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A14" s="30" t="s">
+      <c r="A14" s="33" t="s">
         <v>105</v>
       </c>
       <c r="B14" s="26"/>
@@ -2249,7 +2272,7 @@
       <c r="G14" s="7"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A15" s="30"/>
+      <c r="A15" s="33"/>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
@@ -2258,7 +2281,7 @@
       <c r="G15" s="7"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A16" s="30"/>
+      <c r="A16" s="33"/>
       <c r="B16" s="15"/>
       <c r="C16" s="15"/>
       <c r="D16" s="15"/>
@@ -2267,7 +2290,7 @@
       <c r="G16" s="7"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A17" s="30"/>
+      <c r="A17" s="33"/>
       <c r="B17" s="15"/>
       <c r="C17" s="15"/>
       <c r="D17" s="15"/>
@@ -2276,7 +2299,7 @@
       <c r="G17" s="7"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A18" s="30"/>
+      <c r="A18" s="33"/>
       <c r="B18" s="15"/>
       <c r="C18" s="15"/>
       <c r="D18" s="15"/>
@@ -2285,7 +2308,7 @@
       <c r="G18" s="7"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A19" s="30" t="s">
+      <c r="A19" s="33" t="s">
         <v>104</v>
       </c>
       <c r="B19" s="26"/>
@@ -2296,7 +2319,7 @@
       <c r="G19" s="7"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A20" s="30"/>
+      <c r="A20" s="33"/>
       <c r="B20" s="26"/>
       <c r="C20" s="8"/>
       <c r="D20" s="8"/>
@@ -2305,7 +2328,7 @@
       <c r="G20" s="7"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A21" s="30"/>
+      <c r="A21" s="33"/>
       <c r="B21" s="26"/>
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
@@ -2314,7 +2337,7 @@
       <c r="G21" s="7"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A22" s="30"/>
+      <c r="A22" s="33"/>
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
       <c r="D22" s="11"/>
@@ -2323,7 +2346,7 @@
       <c r="G22" s="7"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A23" s="30"/>
+      <c r="A23" s="33"/>
       <c r="B23" s="9"/>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
@@ -2332,7 +2355,7 @@
       <c r="G23" s="7"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A24" s="30"/>
+      <c r="A24" s="33"/>
       <c r="B24" s="9"/>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
@@ -2341,7 +2364,7 @@
       <c r="G24" s="7"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A25" s="30"/>
+      <c r="A25" s="33"/>
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
@@ -2350,7 +2373,7 @@
       <c r="G25" s="7"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A26" s="30"/>
+      <c r="A26" s="33"/>
       <c r="B26" s="9"/>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
@@ -2359,7 +2382,7 @@
       <c r="G26" s="7"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A27" s="30"/>
+      <c r="A27" s="33"/>
       <c r="B27" s="9"/>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
@@ -2368,7 +2391,7 @@
       <c r="G27" s="7"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A28" s="30"/>
+      <c r="A28" s="33"/>
       <c r="B28" s="9"/>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
@@ -2377,7 +2400,7 @@
       <c r="G28" s="7"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A29" s="30"/>
+      <c r="A29" s="33"/>
       <c r="B29" s="9"/>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
@@ -2386,7 +2409,7 @@
       <c r="G29" s="7"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A30" s="30" t="s">
+      <c r="A30" s="33" t="s">
         <v>47</v>
       </c>
       <c r="B30" s="9"/>
@@ -2397,7 +2420,7 @@
       <c r="G30" s="7"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A31" s="30"/>
+      <c r="A31" s="33"/>
       <c r="B31" s="9"/>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
@@ -2406,7 +2429,7 @@
       <c r="G31" s="7"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A32" s="30"/>
+      <c r="A32" s="33"/>
       <c r="B32" s="15"/>
       <c r="C32" s="15"/>
       <c r="D32" s="15"/>
@@ -2415,7 +2438,7 @@
       <c r="G32" s="7"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A33" s="30"/>
+      <c r="A33" s="33"/>
       <c r="B33" s="15"/>
       <c r="C33" s="15"/>
       <c r="D33" s="15"/>
@@ -2424,7 +2447,7 @@
       <c r="G33" s="7"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A34" s="30"/>
+      <c r="A34" s="33"/>
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
@@ -2433,7 +2456,7 @@
       <c r="G34" s="7"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A35" s="30"/>
+      <c r="A35" s="33"/>
       <c r="B35" s="26"/>
       <c r="C35" s="26"/>
       <c r="D35" s="26"/>
@@ -2483,15 +2506,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
+      <c r="A1" s="32" t="s">
+        <v>137</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
@@ -2503,13 +2526,13 @@
       <c r="P1" s="2"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A2" s="29"/>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
+      <c r="A2" s="32"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
@@ -2521,13 +2544,13 @@
       <c r="P2" s="2"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A3" s="29"/>
-      <c r="B3" s="29"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
+      <c r="A3" s="32"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
@@ -2569,17 +2592,17 @@
       <c r="P4" s="2"/>
     </row>
     <row r="5" spans="1:16" ht="18.75" x14ac:dyDescent="0.15">
-      <c r="A5" s="33" t="s">
-        <v>142</v>
-      </c>
-      <c r="B5" s="34" t="s">
-        <v>144</v>
-      </c>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="32"/>
+      <c r="A5" s="34" t="s">
+        <v>138</v>
+      </c>
+      <c r="B5" s="36" t="s">
+        <v>140</v>
+      </c>
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="36"/>
+      <c r="G5" s="31"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
@@ -2592,12 +2615,12 @@
     </row>
     <row r="6" spans="1:16" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="35"/>
-      <c r="B6" s="34"/>
-      <c r="C6" s="34"/>
-      <c r="D6" s="34"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="34"/>
-      <c r="G6" s="32"/>
+      <c r="B6" s="36"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="36"/>
+      <c r="E6" s="36"/>
+      <c r="F6" s="36"/>
+      <c r="G6" s="31"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
@@ -2609,7 +2632,7 @@
       <c r="P6" s="2"/>
     </row>
     <row r="7" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="30" t="s">
+      <c r="A7" s="33" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="9"/>
@@ -2629,7 +2652,7 @@
       <c r="P7" s="2"/>
     </row>
     <row r="8" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="30"/>
+      <c r="A8" s="33"/>
       <c r="B8" s="27"/>
       <c r="C8" s="27"/>
       <c r="D8" s="27"/>
@@ -2646,8 +2669,8 @@
       <c r="P8" s="2"/>
     </row>
     <row r="9" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="30" t="s">
-        <v>143</v>
+      <c r="A9" s="33" t="s">
+        <v>139</v>
       </c>
       <c r="B9" s="27"/>
       <c r="C9" s="27"/>
@@ -2665,7 +2688,7 @@
       <c r="P9" s="2"/>
     </row>
     <row r="10" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="30"/>
+      <c r="A10" s="33"/>
       <c r="B10" s="27"/>
       <c r="C10" s="27"/>
       <c r="D10" s="27"/>
@@ -2682,7 +2705,7 @@
       <c r="P10" s="2"/>
     </row>
     <row r="11" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="30"/>
+      <c r="A11" s="33"/>
       <c r="B11" s="27"/>
       <c r="C11" s="27"/>
       <c r="D11" s="27"/>
@@ -2699,7 +2722,7 @@
       <c r="P11" s="2"/>
     </row>
     <row r="12" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="30"/>
+      <c r="A12" s="33"/>
       <c r="B12" s="27"/>
       <c r="C12" s="27"/>
       <c r="D12" s="27"/>
@@ -2716,7 +2739,7 @@
       <c r="P12" s="2"/>
     </row>
     <row r="13" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="29" t="s">
+      <c r="A13" s="32" t="s">
         <v>11</v>
       </c>
       <c r="B13" s="13"/>
@@ -2735,7 +2758,7 @@
       <c r="P13" s="2"/>
     </row>
     <row r="14" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="29"/>
+      <c r="A14" s="32"/>
       <c r="B14" s="27"/>
       <c r="C14" s="27"/>
       <c r="D14" s="27"/>
@@ -2752,7 +2775,7 @@
       <c r="P14" s="2"/>
     </row>
     <row r="15" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="29"/>
+      <c r="A15" s="32"/>
       <c r="B15" s="27"/>
       <c r="C15" s="27"/>
       <c r="D15" s="27"/>
@@ -2770,7 +2793,7 @@
       <c r="P15" s="2"/>
     </row>
     <row r="16" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="29"/>
+      <c r="A16" s="32"/>
       <c r="B16" s="27"/>
       <c r="C16" s="27"/>
       <c r="D16" s="27"/>
@@ -2788,7 +2811,7 @@
       <c r="P16" s="2"/>
     </row>
     <row r="17" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="29" t="s">
+      <c r="A17" s="32" t="s">
         <v>22</v>
       </c>
       <c r="B17" s="13"/>
@@ -2808,7 +2831,7 @@
       <c r="P17" s="2"/>
     </row>
     <row r="18" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="29"/>
+      <c r="A18" s="32"/>
       <c r="B18" s="27"/>
       <c r="C18" s="27"/>
       <c r="D18" s="27"/>
@@ -2826,7 +2849,7 @@
       <c r="P18" s="27"/>
     </row>
     <row r="19" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="29"/>
+      <c r="A19" s="32"/>
       <c r="B19" s="9"/>
       <c r="C19" s="10"/>
       <c r="D19" s="11"/>
@@ -2844,7 +2867,7 @@
       <c r="P19" s="27"/>
     </row>
     <row r="20" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="30" t="s">
+      <c r="A20" s="33" t="s">
         <v>105</v>
       </c>
       <c r="B20" s="28"/>
@@ -2864,7 +2887,7 @@
       <c r="P20" s="27"/>
     </row>
     <row r="21" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="30"/>
+      <c r="A21" s="33"/>
       <c r="B21" s="9"/>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
@@ -2882,7 +2905,7 @@
       <c r="P21" s="27"/>
     </row>
     <row r="22" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="30"/>
+      <c r="A22" s="33"/>
       <c r="B22" s="15"/>
       <c r="C22" s="15"/>
       <c r="D22" s="15"/>
@@ -2900,7 +2923,7 @@
       <c r="P22" s="27"/>
     </row>
     <row r="23" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="30"/>
+      <c r="A23" s="33"/>
       <c r="B23" s="15"/>
       <c r="C23" s="15"/>
       <c r="D23" s="15"/>
@@ -2909,7 +2932,7 @@
       <c r="G23" s="7"/>
     </row>
     <row r="24" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="30"/>
+      <c r="A24" s="33"/>
       <c r="B24" s="15"/>
       <c r="C24" s="15"/>
       <c r="D24" s="15"/>
@@ -2918,7 +2941,7 @@
       <c r="G24" s="7"/>
     </row>
     <row r="25" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="30" t="s">
+      <c r="A25" s="33" t="s">
         <v>104</v>
       </c>
       <c r="B25" s="28"/>
@@ -2929,7 +2952,7 @@
       <c r="G25" s="7"/>
     </row>
     <row r="26" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="30"/>
+      <c r="A26" s="33"/>
       <c r="B26" s="28"/>
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
@@ -2938,7 +2961,7 @@
       <c r="G26" s="7"/>
     </row>
     <row r="27" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="30"/>
+      <c r="A27" s="33"/>
       <c r="B27" s="28"/>
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
@@ -2947,7 +2970,7 @@
       <c r="G27" s="7"/>
     </row>
     <row r="28" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="30"/>
+      <c r="A28" s="33"/>
       <c r="B28" s="9"/>
       <c r="C28" s="9"/>
       <c r="D28" s="11"/>
@@ -2956,7 +2979,7 @@
       <c r="G28" s="7"/>
     </row>
     <row r="29" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="30"/>
+      <c r="A29" s="33"/>
       <c r="B29" s="9"/>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
@@ -2965,7 +2988,7 @@
       <c r="G29" s="7"/>
     </row>
     <row r="30" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="30"/>
+      <c r="A30" s="33"/>
       <c r="B30" s="9"/>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
@@ -2974,7 +2997,7 @@
       <c r="G30" s="7"/>
     </row>
     <row r="31" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="30"/>
+      <c r="A31" s="33"/>
       <c r="B31" s="9"/>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
@@ -2983,7 +3006,7 @@
       <c r="G31" s="7"/>
     </row>
     <row r="32" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="30"/>
+      <c r="A32" s="33"/>
       <c r="B32" s="9"/>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
@@ -2992,7 +3015,7 @@
       <c r="G32" s="7"/>
     </row>
     <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="30"/>
+      <c r="A33" s="33"/>
       <c r="B33" s="9"/>
       <c r="C33" s="9"/>
       <c r="D33" s="9"/>
@@ -3001,7 +3024,7 @@
       <c r="G33" s="7"/>
     </row>
     <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="30"/>
+      <c r="A34" s="33"/>
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
@@ -3010,7 +3033,7 @@
       <c r="G34" s="7"/>
     </row>
     <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="30"/>
+      <c r="A35" s="33"/>
       <c r="B35" s="9"/>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
@@ -3019,7 +3042,7 @@
       <c r="G35" s="7"/>
     </row>
     <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="30" t="s">
+      <c r="A36" s="33" t="s">
         <v>47</v>
       </c>
       <c r="B36" s="9"/>
@@ -3030,7 +3053,7 @@
       <c r="G36" s="7"/>
     </row>
     <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="30"/>
+      <c r="A37" s="33"/>
       <c r="B37" s="9"/>
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
@@ -3039,7 +3062,7 @@
       <c r="G37" s="7"/>
     </row>
     <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="30"/>
+      <c r="A38" s="33"/>
       <c r="B38" s="15"/>
       <c r="C38" s="15"/>
       <c r="D38" s="15"/>
@@ -3048,7 +3071,7 @@
       <c r="G38" s="7"/>
     </row>
     <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A39" s="30"/>
+      <c r="A39" s="33"/>
       <c r="B39" s="15"/>
       <c r="C39" s="15"/>
       <c r="D39" s="15"/>
@@ -3056,7 +3079,7 @@
       <c r="F39" s="15"/>
     </row>
     <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="30"/>
+      <c r="A40" s="33"/>
       <c r="B40" s="9"/>
       <c r="C40" s="9"/>
       <c r="D40" s="9"/>
@@ -3064,7 +3087,7 @@
       <c r="F40" s="9"/>
     </row>
     <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A41" s="30"/>
+      <c r="A41" s="33"/>
       <c r="B41" s="28"/>
       <c r="C41" s="28"/>
       <c r="D41" s="28"/>
@@ -3118,585 +3141,606 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:R62"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="19.125" customWidth="1"/>
+    <col min="4" max="4" width="15.75" customWidth="1"/>
+    <col min="5" max="5" width="17" customWidth="1"/>
+    <col min="6" max="6" width="116.875" customWidth="1"/>
+    <col min="7" max="7" width="2.25" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A1" s="31" t="s">
-        <v>126</v>
-      </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="23"/>
+    <row r="1" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="32" t="s">
+        <v>141</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
+      <c r="N1" s="37"/>
+      <c r="O1" s="37"/>
+      <c r="P1" s="37"/>
+      <c r="Q1" s="37"/>
       <c r="R1" s="23"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A2" s="29"/>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
-      <c r="K2" s="29"/>
-      <c r="L2" s="29"/>
-      <c r="M2" s="29"/>
-      <c r="N2" s="29"/>
-      <c r="O2" s="29"/>
-      <c r="P2" s="29"/>
-      <c r="Q2" s="23"/>
+    <row r="2" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="32"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
+      <c r="J2" s="37"/>
+      <c r="K2" s="37"/>
+      <c r="L2" s="37"/>
+      <c r="M2" s="37"/>
+      <c r="N2" s="37"/>
+      <c r="O2" s="37"/>
+      <c r="P2" s="37"/>
+      <c r="Q2" s="37"/>
       <c r="R2" s="23"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A3" s="29"/>
-      <c r="B3" s="29"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="29"/>
-      <c r="K3" s="29"/>
-      <c r="L3" s="29"/>
-      <c r="M3" s="29"/>
-      <c r="N3" s="29"/>
-      <c r="O3" s="29"/>
-      <c r="P3" s="29"/>
-      <c r="Q3" s="23"/>
+    <row r="3" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="32"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="37"/>
+      <c r="I3" s="37"/>
+      <c r="J3" s="37"/>
+      <c r="K3" s="37"/>
+      <c r="L3" s="37"/>
+      <c r="M3" s="37"/>
+      <c r="N3" s="37"/>
+      <c r="O3" s="37"/>
+      <c r="P3" s="37"/>
+      <c r="Q3" s="37"/>
       <c r="R3" s="23"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A4" s="29" t="s">
-        <v>118</v>
-      </c>
-      <c r="B4" s="29"/>
-      <c r="C4" s="29" t="s">
-        <v>120</v>
-      </c>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
-      <c r="I4" s="29"/>
-      <c r="J4" s="29"/>
-      <c r="K4" s="29"/>
-      <c r="L4" s="29"/>
-      <c r="M4" s="29"/>
-      <c r="N4" s="29"/>
-      <c r="O4" s="29"/>
-      <c r="P4" s="29"/>
-      <c r="Q4" s="23"/>
+    <row r="4" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="5"/>
+      <c r="H4" s="37"/>
+      <c r="I4" s="37"/>
+      <c r="J4" s="37"/>
+      <c r="K4" s="37"/>
+      <c r="L4" s="37"/>
+      <c r="M4" s="37"/>
+      <c r="N4" s="37"/>
+      <c r="O4" s="37"/>
+      <c r="P4" s="37"/>
+      <c r="Q4" s="37"/>
       <c r="R4" s="23"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A5" s="29"/>
-      <c r="B5" s="29"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="29"/>
-      <c r="J5" s="29"/>
-      <c r="K5" s="29"/>
-      <c r="L5" s="29"/>
-      <c r="M5" s="29"/>
-      <c r="N5" s="29"/>
-      <c r="O5" s="29"/>
-      <c r="P5" s="29"/>
-      <c r="Q5" s="23"/>
+    <row r="5" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="34" t="s">
+        <v>138</v>
+      </c>
+      <c r="B5" s="36" t="s">
+        <v>142</v>
+      </c>
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="36"/>
+      <c r="G5" s="31"/>
+      <c r="H5" s="37"/>
+      <c r="I5" s="37"/>
+      <c r="J5" s="37"/>
+      <c r="K5" s="37"/>
+      <c r="L5" s="37"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="37"/>
+      <c r="O5" s="37"/>
+      <c r="P5" s="37"/>
+      <c r="Q5" s="37"/>
       <c r="R5" s="23"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A6" s="29" t="s">
-        <v>119</v>
-      </c>
-      <c r="B6" s="29"/>
-      <c r="C6" s="29" t="s">
-        <v>121</v>
-      </c>
-      <c r="D6" s="29"/>
-      <c r="E6" s="29"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="29"/>
-      <c r="H6" s="29"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="29"/>
-      <c r="K6" s="29"/>
-      <c r="L6" s="29"/>
-      <c r="M6" s="29"/>
-      <c r="N6" s="29"/>
-      <c r="O6" s="29"/>
-      <c r="P6" s="29"/>
-      <c r="Q6" s="23"/>
+    <row r="6" spans="1:18" ht="32.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="35"/>
+      <c r="B6" s="36"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="36"/>
+      <c r="E6" s="36"/>
+      <c r="F6" s="36"/>
+      <c r="G6" s="31"/>
+      <c r="H6" s="37"/>
+      <c r="I6" s="37"/>
+      <c r="J6" s="37"/>
+      <c r="K6" s="37"/>
+      <c r="L6" s="37"/>
+      <c r="M6" s="37"/>
+      <c r="N6" s="37"/>
+      <c r="O6" s="37"/>
+      <c r="P6" s="37"/>
+      <c r="Q6" s="37"/>
       <c r="R6" s="23"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A7" s="29"/>
-      <c r="B7" s="29"/>
-      <c r="C7" s="29"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="29"/>
-      <c r="H7" s="29"/>
-      <c r="I7" s="29"/>
-      <c r="J7" s="29"/>
-      <c r="K7" s="29"/>
-      <c r="L7" s="29"/>
-      <c r="M7" s="29"/>
-      <c r="N7" s="29"/>
-      <c r="O7" s="29"/>
-      <c r="P7" s="29"/>
-      <c r="Q7" s="23"/>
+    <row r="7" spans="1:18" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="9"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="37"/>
+      <c r="I7" s="37"/>
+      <c r="J7" s="37"/>
+      <c r="K7" s="37"/>
+      <c r="L7" s="37"/>
+      <c r="M7" s="37"/>
+      <c r="N7" s="37"/>
+      <c r="O7" s="37"/>
+      <c r="P7" s="37"/>
+      <c r="Q7" s="37"/>
       <c r="R7" s="23"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A8" s="29"/>
+    <row r="8" spans="1:18" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="33"/>
       <c r="B8" s="29"/>
       <c r="C8" s="29"/>
       <c r="D8" s="29"/>
-      <c r="E8" s="29"/>
+      <c r="E8" s="21"/>
       <c r="F8" s="29"/>
-      <c r="G8" s="29"/>
-      <c r="H8" s="29"/>
-      <c r="I8" s="29"/>
-      <c r="J8" s="29"/>
-      <c r="K8" s="29"/>
-      <c r="L8" s="29"/>
-      <c r="M8" s="29"/>
-      <c r="N8" s="29"/>
-      <c r="O8" s="29"/>
-      <c r="P8" s="29"/>
-      <c r="Q8" s="23"/>
+      <c r="H8" s="37"/>
+      <c r="I8" s="37"/>
+      <c r="J8" s="37"/>
+      <c r="K8" s="37"/>
+      <c r="L8" s="37"/>
+      <c r="M8" s="37"/>
+      <c r="N8" s="37"/>
+      <c r="O8" s="37"/>
+      <c r="P8" s="37"/>
+      <c r="Q8" s="37"/>
       <c r="R8" s="23"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A9" s="29"/>
+    <row r="9" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="33" t="s">
+        <v>118</v>
+      </c>
       <c r="B9" s="29"/>
       <c r="C9" s="29"/>
       <c r="D9" s="29"/>
-      <c r="E9" s="29"/>
+      <c r="E9" s="21"/>
       <c r="F9" s="29"/>
-      <c r="G9" s="29"/>
-      <c r="H9" s="29"/>
-      <c r="I9" s="29"/>
-      <c r="J9" s="29"/>
-      <c r="K9" s="29"/>
-      <c r="L9" s="29"/>
-      <c r="M9" s="29"/>
-      <c r="N9" s="29"/>
-      <c r="O9" s="29"/>
-      <c r="P9" s="29"/>
-      <c r="Q9" s="23"/>
+      <c r="H9" s="37"/>
+      <c r="I9" s="37"/>
+      <c r="J9" s="37"/>
+      <c r="K9" s="37"/>
+      <c r="L9" s="37"/>
+      <c r="M9" s="37"/>
+      <c r="N9" s="37"/>
+      <c r="O9" s="37"/>
+      <c r="P9" s="37"/>
+      <c r="Q9" s="37"/>
       <c r="R9" s="23"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A10" s="29"/>
+    <row r="10" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="33"/>
       <c r="B10" s="29"/>
       <c r="C10" s="29"/>
       <c r="D10" s="29"/>
-      <c r="E10" s="29"/>
+      <c r="E10" s="21"/>
       <c r="F10" s="29"/>
-      <c r="G10" s="29"/>
-      <c r="H10" s="29"/>
-      <c r="I10" s="29"/>
-      <c r="J10" s="29"/>
-      <c r="K10" s="29"/>
-      <c r="L10" s="29"/>
-      <c r="M10" s="29"/>
-      <c r="N10" s="29"/>
-      <c r="O10" s="29"/>
-      <c r="P10" s="29"/>
-      <c r="Q10" s="23"/>
+      <c r="H10" s="37"/>
+      <c r="I10" s="37"/>
+      <c r="J10" s="37"/>
+      <c r="K10" s="37"/>
+      <c r="L10" s="37"/>
+      <c r="M10" s="37"/>
+      <c r="N10" s="37"/>
+      <c r="O10" s="37"/>
+      <c r="P10" s="37"/>
+      <c r="Q10" s="37"/>
       <c r="R10" s="23"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A11" s="29"/>
+    <row r="11" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="33"/>
       <c r="B11" s="29"/>
       <c r="C11" s="29"/>
       <c r="D11" s="29"/>
-      <c r="E11" s="29"/>
+      <c r="E11" s="21"/>
       <c r="F11" s="29"/>
-      <c r="G11" s="29"/>
-      <c r="H11" s="29"/>
-      <c r="I11" s="29"/>
-      <c r="J11" s="29"/>
-      <c r="K11" s="29"/>
-      <c r="L11" s="29"/>
-      <c r="M11" s="29"/>
-      <c r="N11" s="29"/>
-      <c r="O11" s="29"/>
-      <c r="P11" s="29"/>
-      <c r="Q11" s="23"/>
+      <c r="H11" s="37"/>
+      <c r="I11" s="37"/>
+      <c r="J11" s="37"/>
+      <c r="K11" s="37"/>
+      <c r="L11" s="37"/>
+      <c r="M11" s="37"/>
+      <c r="N11" s="37"/>
+      <c r="O11" s="37"/>
+      <c r="P11" s="37"/>
+      <c r="Q11" s="37"/>
       <c r="R11" s="23"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A12" s="29"/>
+    <row r="12" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="33"/>
       <c r="B12" s="29"/>
       <c r="C12" s="29"/>
       <c r="D12" s="29"/>
-      <c r="E12" s="29"/>
+      <c r="E12" s="21"/>
       <c r="F12" s="29"/>
-      <c r="G12" s="29"/>
-      <c r="H12" s="29"/>
-      <c r="I12" s="29"/>
-      <c r="J12" s="29"/>
-      <c r="K12" s="29"/>
-      <c r="L12" s="29"/>
-      <c r="M12" s="29"/>
-      <c r="N12" s="29"/>
-      <c r="O12" s="29"/>
-      <c r="P12" s="29"/>
-      <c r="Q12" s="23"/>
+      <c r="H12" s="37"/>
+      <c r="I12" s="37"/>
+      <c r="J12" s="37"/>
+      <c r="K12" s="37"/>
+      <c r="L12" s="37"/>
+      <c r="M12" s="37"/>
+      <c r="N12" s="37"/>
+      <c r="O12" s="37"/>
+      <c r="P12" s="37"/>
+      <c r="Q12" s="37"/>
       <c r="R12" s="23"/>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A13" s="29"/>
-      <c r="B13" s="29"/>
-      <c r="C13" s="29"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="29"/>
-      <c r="G13" s="29"/>
-      <c r="H13" s="29"/>
-      <c r="I13" s="29"/>
-      <c r="J13" s="29"/>
-      <c r="K13" s="29"/>
-      <c r="L13" s="29"/>
-      <c r="M13" s="29"/>
-      <c r="N13" s="29"/>
-      <c r="O13" s="29"/>
-      <c r="P13" s="29"/>
-      <c r="Q13" s="23"/>
+    <row r="13" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="9"/>
+      <c r="H13" s="37"/>
+      <c r="I13" s="37"/>
+      <c r="J13" s="37"/>
+      <c r="K13" s="37"/>
+      <c r="L13" s="37"/>
+      <c r="M13" s="37"/>
+      <c r="N13" s="37"/>
+      <c r="O13" s="37"/>
+      <c r="P13" s="37"/>
+      <c r="Q13" s="37"/>
       <c r="R13" s="23"/>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A14" s="29"/>
+    <row r="14" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="32"/>
       <c r="B14" s="29"/>
       <c r="C14" s="29"/>
       <c r="D14" s="29"/>
-      <c r="E14" s="29"/>
+      <c r="E14" s="21"/>
       <c r="F14" s="29"/>
-      <c r="G14" s="29"/>
-      <c r="H14" s="29"/>
-      <c r="I14" s="29"/>
-      <c r="J14" s="29"/>
-      <c r="K14" s="29"/>
-      <c r="L14" s="29"/>
-      <c r="M14" s="29"/>
-      <c r="N14" s="29"/>
-      <c r="O14" s="29"/>
-      <c r="P14" s="29"/>
-      <c r="Q14" s="23"/>
+      <c r="H14" s="37"/>
+      <c r="I14" s="37"/>
+      <c r="J14" s="37"/>
+      <c r="K14" s="37"/>
+      <c r="L14" s="37"/>
+      <c r="M14" s="37"/>
+      <c r="N14" s="37"/>
+      <c r="O14" s="37"/>
+      <c r="P14" s="37"/>
+      <c r="Q14" s="37"/>
       <c r="R14" s="23"/>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A15" s="29"/>
+    <row r="15" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="32"/>
       <c r="B15" s="29"/>
       <c r="C15" s="29"/>
       <c r="D15" s="29"/>
-      <c r="E15" s="29"/>
+      <c r="E15" s="21"/>
       <c r="F15" s="29"/>
-      <c r="G15" s="29"/>
-      <c r="H15" s="29"/>
-      <c r="I15" s="29"/>
-      <c r="J15" s="29"/>
-      <c r="K15" s="29"/>
-      <c r="L15" s="29"/>
-      <c r="M15" s="29"/>
-      <c r="N15" s="29"/>
-      <c r="O15" s="29"/>
-      <c r="P15" s="29"/>
-      <c r="Q15" s="23"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="37"/>
+      <c r="I15" s="37"/>
+      <c r="J15" s="37"/>
+      <c r="K15" s="37"/>
+      <c r="L15" s="37"/>
+      <c r="M15" s="37"/>
+      <c r="N15" s="37"/>
+      <c r="O15" s="37"/>
+      <c r="P15" s="37"/>
+      <c r="Q15" s="37"/>
       <c r="R15" s="23"/>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A16" s="29"/>
+    <row r="16" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="32"/>
       <c r="B16" s="29"/>
-      <c r="C16" s="23"/>
-      <c r="D16" s="23"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="23"/>
-      <c r="G16" s="23"/>
-      <c r="H16" s="23"/>
-      <c r="I16" s="23"/>
-      <c r="J16" s="23"/>
-      <c r="K16" s="23"/>
-      <c r="L16" s="23"/>
-      <c r="M16" s="23"/>
-      <c r="N16" s="23"/>
-      <c r="O16" s="23"/>
-      <c r="P16" s="23"/>
-      <c r="Q16" s="23"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="29"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="29"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="37"/>
+      <c r="I16" s="37"/>
+      <c r="J16" s="37"/>
+      <c r="K16" s="37"/>
+      <c r="L16" s="37"/>
+      <c r="M16" s="37"/>
+      <c r="N16" s="37"/>
+      <c r="O16" s="37"/>
+      <c r="P16" s="37"/>
+      <c r="Q16" s="37"/>
       <c r="R16" s="23"/>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A17" s="29"/>
-      <c r="B17" s="29"/>
-      <c r="C17" s="23"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="23"/>
-      <c r="F17" s="23"/>
-      <c r="G17" s="23"/>
-      <c r="H17" s="23"/>
-      <c r="I17" s="23"/>
-      <c r="J17" s="23"/>
-      <c r="K17" s="23"/>
-      <c r="L17" s="23"/>
-      <c r="M17" s="23"/>
-      <c r="N17" s="23"/>
-      <c r="O17" s="23"/>
-      <c r="P17" s="23"/>
-      <c r="Q17" s="23"/>
+    <row r="17" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="37"/>
+      <c r="I17" s="37"/>
+      <c r="J17" s="37"/>
+      <c r="K17" s="37"/>
+      <c r="L17" s="37"/>
+      <c r="M17" s="37"/>
+      <c r="N17" s="37"/>
+      <c r="O17" s="37"/>
+      <c r="P17" s="37"/>
+      <c r="Q17" s="37"/>
       <c r="R17" s="23"/>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A18" s="29"/>
+    <row r="18" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="32"/>
       <c r="B18" s="29"/>
-      <c r="C18" s="23"/>
-      <c r="D18" s="23"/>
-      <c r="E18" s="23"/>
-      <c r="F18" s="23"/>
-      <c r="G18" s="23"/>
-      <c r="H18" s="23"/>
-      <c r="I18" s="23"/>
-      <c r="J18" s="23"/>
-      <c r="K18" s="23"/>
-      <c r="L18" s="23"/>
-      <c r="M18" s="23"/>
-      <c r="N18" s="23"/>
-      <c r="O18" s="23"/>
-      <c r="P18" s="23"/>
-      <c r="Q18" s="23"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="29"/>
+      <c r="E18" s="29"/>
+      <c r="F18" s="30"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="37"/>
+      <c r="I18" s="37"/>
+      <c r="J18" s="37"/>
+      <c r="K18" s="37"/>
+      <c r="L18" s="37"/>
+      <c r="M18" s="37"/>
+      <c r="N18" s="37"/>
+      <c r="O18" s="37"/>
+      <c r="P18" s="37"/>
+      <c r="Q18" s="37"/>
       <c r="R18" s="23"/>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A19" s="29"/>
-      <c r="B19" s="29"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="23"/>
-      <c r="H19" s="23"/>
-      <c r="I19" s="23"/>
-      <c r="J19" s="23"/>
-      <c r="K19" s="23"/>
-      <c r="L19" s="23"/>
-      <c r="M19" s="23"/>
-      <c r="N19" s="23"/>
-      <c r="O19" s="23"/>
-      <c r="P19" s="23"/>
-      <c r="Q19" s="23"/>
+    <row r="19" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="32"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="37"/>
+      <c r="I19" s="37"/>
+      <c r="J19" s="37"/>
+      <c r="K19" s="37"/>
+      <c r="L19" s="37"/>
+      <c r="M19" s="37"/>
+      <c r="N19" s="37"/>
+      <c r="O19" s="37"/>
+      <c r="P19" s="37"/>
+      <c r="Q19" s="37"/>
       <c r="R19" s="23"/>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A20" s="29"/>
-      <c r="B20" s="29"/>
-      <c r="C20" s="23"/>
-      <c r="D20" s="23"/>
-      <c r="E20" s="23"/>
-      <c r="F20" s="23"/>
-      <c r="G20" s="23"/>
-      <c r="H20" s="23"/>
-      <c r="I20" s="23"/>
-      <c r="J20" s="23"/>
-      <c r="K20" s="23"/>
-      <c r="L20" s="23"/>
-      <c r="M20" s="23"/>
-      <c r="N20" s="23"/>
-      <c r="O20" s="23"/>
-      <c r="P20" s="23"/>
-      <c r="Q20" s="23"/>
+    <row r="20" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="33" t="s">
+        <v>105</v>
+      </c>
+      <c r="B20" s="30"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="37"/>
+      <c r="I20" s="37"/>
+      <c r="J20" s="37"/>
+      <c r="K20" s="37"/>
+      <c r="L20" s="37"/>
+      <c r="M20" s="37"/>
+      <c r="N20" s="37"/>
+      <c r="O20" s="37"/>
+      <c r="P20" s="37"/>
+      <c r="Q20" s="37"/>
       <c r="R20" s="23"/>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A21" s="23"/>
-      <c r="B21" s="23"/>
-      <c r="C21" s="23"/>
-      <c r="D21" s="23"/>
-      <c r="E21" s="23"/>
-      <c r="F21" s="23"/>
-      <c r="G21" s="23"/>
-      <c r="H21" s="23"/>
-      <c r="I21" s="23"/>
-      <c r="J21" s="23"/>
-      <c r="K21" s="23"/>
-      <c r="L21" s="23"/>
-      <c r="M21" s="23"/>
-      <c r="N21" s="23"/>
-      <c r="O21" s="23"/>
-      <c r="P21" s="23"/>
-      <c r="Q21" s="23"/>
+    <row r="21" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="33"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="37"/>
+      <c r="I21" s="37"/>
+      <c r="J21" s="37"/>
+      <c r="K21" s="37"/>
+      <c r="L21" s="37"/>
+      <c r="M21" s="37"/>
+      <c r="N21" s="37"/>
+      <c r="O21" s="37"/>
+      <c r="P21" s="37"/>
+      <c r="Q21" s="37"/>
       <c r="R21" s="23"/>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A22" s="23"/>
-      <c r="B22" s="23"/>
-      <c r="C22" s="23"/>
-      <c r="D22" s="23"/>
-      <c r="E22" s="23"/>
-      <c r="F22" s="23"/>
-      <c r="G22" s="23"/>
-      <c r="H22" s="23"/>
-      <c r="I22" s="23"/>
-      <c r="J22" s="23"/>
-      <c r="K22" s="23"/>
-      <c r="L22" s="23"/>
-      <c r="M22" s="23"/>
-      <c r="N22" s="23"/>
-      <c r="O22" s="23"/>
-      <c r="P22" s="23"/>
-      <c r="Q22" s="23"/>
+    <row r="22" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="33"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="37"/>
+      <c r="I22" s="37"/>
+      <c r="J22" s="37"/>
+      <c r="K22" s="37"/>
+      <c r="L22" s="37"/>
+      <c r="M22" s="37"/>
+      <c r="N22" s="37"/>
+      <c r="O22" s="37"/>
+      <c r="P22" s="37"/>
+      <c r="Q22" s="37"/>
       <c r="R22" s="23"/>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A23" s="23"/>
-      <c r="B23" s="23"/>
-      <c r="C23" s="23"/>
-      <c r="D23" s="23"/>
-      <c r="E23" s="23"/>
-      <c r="F23" s="23"/>
-      <c r="G23" s="23"/>
-      <c r="H23" s="23"/>
-      <c r="I23" s="23"/>
-      <c r="J23" s="23"/>
-      <c r="K23" s="23"/>
-      <c r="L23" s="23"/>
-      <c r="M23" s="23"/>
-      <c r="N23" s="23"/>
-      <c r="O23" s="23"/>
-      <c r="P23" s="23"/>
-      <c r="Q23" s="23"/>
+    <row r="23" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="33"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="37"/>
+      <c r="I23" s="37"/>
+      <c r="J23" s="37"/>
+      <c r="K23" s="37"/>
+      <c r="L23" s="37"/>
+      <c r="M23" s="37"/>
+      <c r="N23" s="37"/>
+      <c r="O23" s="37"/>
+      <c r="P23" s="37"/>
+      <c r="Q23" s="37"/>
       <c r="R23" s="23"/>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A24" s="23"/>
-      <c r="B24" s="23"/>
-      <c r="C24" s="23"/>
-      <c r="D24" s="23"/>
-      <c r="E24" s="23"/>
-      <c r="F24" s="23"/>
-      <c r="G24" s="23"/>
-      <c r="H24" s="23"/>
-      <c r="I24" s="23"/>
-      <c r="J24" s="23"/>
-      <c r="K24" s="23"/>
-      <c r="L24" s="23"/>
-      <c r="M24" s="23"/>
-      <c r="N24" s="23"/>
-      <c r="O24" s="23"/>
-      <c r="P24" s="23"/>
-      <c r="Q24" s="23"/>
+    <row r="24" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="33"/>
+      <c r="B24" s="15"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="7"/>
+      <c r="H24" s="37"/>
+      <c r="I24" s="37"/>
+      <c r="J24" s="37"/>
+      <c r="K24" s="37"/>
+      <c r="L24" s="37"/>
+      <c r="M24" s="37"/>
+      <c r="N24" s="37"/>
+      <c r="O24" s="37"/>
+      <c r="P24" s="37"/>
+      <c r="Q24" s="37"/>
       <c r="R24" s="23"/>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A25" s="23"/>
-      <c r="B25" s="23"/>
-      <c r="C25" s="23"/>
-      <c r="D25" s="23"/>
-      <c r="E25" s="23"/>
-      <c r="F25" s="23"/>
-      <c r="G25" s="23"/>
-      <c r="H25" s="23"/>
-      <c r="I25" s="23"/>
-      <c r="J25" s="23"/>
-      <c r="K25" s="23"/>
-      <c r="L25" s="23"/>
-      <c r="M25" s="23"/>
-      <c r="N25" s="23"/>
-      <c r="O25" s="23"/>
-      <c r="P25" s="23"/>
-      <c r="Q25" s="23"/>
+    <row r="25" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="33" t="s">
+        <v>104</v>
+      </c>
+      <c r="B25" s="30"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="30"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="37"/>
+      <c r="I25" s="37"/>
+      <c r="J25" s="37"/>
+      <c r="K25" s="37"/>
+      <c r="L25" s="37"/>
+      <c r="M25" s="37"/>
+      <c r="N25" s="37"/>
+      <c r="O25" s="37"/>
+      <c r="P25" s="37"/>
+      <c r="Q25" s="37"/>
       <c r="R25" s="23"/>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A26" s="23"/>
-      <c r="B26" s="23"/>
-      <c r="C26" s="23"/>
-      <c r="D26" s="23"/>
-      <c r="E26" s="23"/>
-      <c r="F26" s="23"/>
-      <c r="G26" s="23"/>
-      <c r="H26" s="23"/>
-      <c r="I26" s="23"/>
-      <c r="J26" s="23"/>
-      <c r="K26" s="23"/>
-      <c r="L26" s="23"/>
-      <c r="M26" s="23"/>
-      <c r="N26" s="23"/>
-      <c r="O26" s="23"/>
-      <c r="P26" s="23"/>
-      <c r="Q26" s="23"/>
+    <row r="26" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="33"/>
+      <c r="B26" s="30"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="30"/>
+      <c r="G26" s="7"/>
+      <c r="H26" s="37"/>
+      <c r="I26" s="37"/>
+      <c r="J26" s="37"/>
+      <c r="K26" s="37"/>
+      <c r="L26" s="37"/>
+      <c r="M26" s="37"/>
+      <c r="N26" s="37"/>
+      <c r="O26" s="37"/>
+      <c r="P26" s="37"/>
+      <c r="Q26" s="37"/>
       <c r="R26" s="23"/>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A27" s="23"/>
-      <c r="B27" s="23"/>
-      <c r="C27" s="23"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="23"/>
-      <c r="H27" s="23"/>
-      <c r="I27" s="23"/>
-      <c r="J27" s="23"/>
-      <c r="K27" s="23"/>
-      <c r="L27" s="23"/>
-      <c r="M27" s="23"/>
-      <c r="N27" s="23"/>
-      <c r="O27" s="23"/>
-      <c r="P27" s="23"/>
-      <c r="Q27" s="23"/>
+    <row r="27" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="33"/>
+      <c r="B27" s="30"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="30"/>
+      <c r="G27" s="7"/>
+      <c r="H27" s="37"/>
+      <c r="I27" s="37"/>
+      <c r="J27" s="37"/>
+      <c r="K27" s="37"/>
+      <c r="L27" s="37"/>
+      <c r="M27" s="37"/>
+      <c r="N27" s="37"/>
+      <c r="O27" s="37"/>
+      <c r="P27" s="37"/>
+      <c r="Q27" s="37"/>
       <c r="R27" s="23"/>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A28" s="23"/>
-      <c r="B28" s="23"/>
-      <c r="C28" s="23"/>
-      <c r="D28" s="23"/>
-      <c r="E28" s="23"/>
-      <c r="F28" s="23"/>
-      <c r="G28" s="23"/>
-      <c r="H28" s="23"/>
-      <c r="I28" s="23"/>
-      <c r="J28" s="23"/>
-      <c r="K28" s="23"/>
-      <c r="L28" s="23"/>
-      <c r="M28" s="23"/>
-      <c r="N28" s="23"/>
-      <c r="O28" s="23"/>
-      <c r="P28" s="23"/>
-      <c r="Q28" s="23"/>
+    <row r="28" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="33"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="37"/>
+      <c r="I28" s="37"/>
+      <c r="J28" s="37"/>
+      <c r="K28" s="37"/>
+      <c r="L28" s="37"/>
+      <c r="M28" s="37"/>
+      <c r="N28" s="37"/>
+      <c r="O28" s="37"/>
+      <c r="P28" s="37"/>
+      <c r="Q28" s="37"/>
       <c r="R28" s="23"/>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A29" s="23"/>
-      <c r="B29" s="23"/>
-      <c r="C29" s="23"/>
-      <c r="D29" s="23"/>
-      <c r="E29" s="23"/>
-      <c r="F29" s="23"/>
-      <c r="G29" s="23"/>
+      <c r="A29" s="33"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="7"/>
       <c r="H29" s="23"/>
       <c r="I29" s="23"/>
       <c r="J29" s="23"/>
@@ -3710,13 +3754,13 @@
       <c r="R29" s="23"/>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A30" s="23"/>
-      <c r="B30" s="23"/>
-      <c r="C30" s="23"/>
-      <c r="D30" s="23"/>
-      <c r="E30" s="23"/>
-      <c r="F30" s="23"/>
-      <c r="G30" s="23"/>
+      <c r="A30" s="33"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="7"/>
       <c r="H30" s="23"/>
       <c r="I30" s="23"/>
       <c r="J30" s="23"/>
@@ -3730,13 +3774,13 @@
       <c r="R30" s="23"/>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A31" s="23"/>
-      <c r="B31" s="23"/>
-      <c r="C31" s="23"/>
-      <c r="D31" s="23"/>
-      <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
-      <c r="G31" s="23"/>
+      <c r="A31" s="33"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="7"/>
       <c r="H31" s="23"/>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
@@ -3750,13 +3794,13 @@
       <c r="R31" s="23"/>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A32" s="23"/>
-      <c r="B32" s="23"/>
-      <c r="C32" s="23"/>
-      <c r="D32" s="23"/>
-      <c r="E32" s="23"/>
-      <c r="F32" s="23"/>
-      <c r="G32" s="23"/>
+      <c r="A32" s="33"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="7"/>
       <c r="H32" s="23"/>
       <c r="I32" s="23"/>
       <c r="J32" s="23"/>
@@ -3770,13 +3814,13 @@
       <c r="R32" s="23"/>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A33" s="23"/>
-      <c r="B33" s="23"/>
-      <c r="C33" s="23"/>
-      <c r="D33" s="23"/>
-      <c r="E33" s="23"/>
-      <c r="F33" s="23"/>
-      <c r="G33" s="23"/>
+      <c r="A33" s="33"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="7"/>
       <c r="H33" s="23"/>
       <c r="I33" s="23"/>
       <c r="J33" s="23"/>
@@ -3790,13 +3834,13 @@
       <c r="R33" s="23"/>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A34" s="23"/>
-      <c r="B34" s="23"/>
-      <c r="C34" s="23"/>
-      <c r="D34" s="23"/>
-      <c r="E34" s="23"/>
-      <c r="F34" s="23"/>
-      <c r="G34" s="23"/>
+      <c r="A34" s="33"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="12"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="7"/>
       <c r="H34" s="23"/>
       <c r="I34" s="23"/>
       <c r="J34" s="23"/>
@@ -3810,13 +3854,13 @@
       <c r="R34" s="23"/>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A35" s="23"/>
-      <c r="B35" s="23"/>
-      <c r="C35" s="23"/>
-      <c r="D35" s="23"/>
-      <c r="E35" s="23"/>
-      <c r="F35" s="23"/>
-      <c r="G35" s="23"/>
+      <c r="A35" s="33"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="9"/>
+      <c r="G35" s="7"/>
       <c r="H35" s="23"/>
       <c r="I35" s="23"/>
       <c r="J35" s="23"/>
@@ -3830,13 +3874,15 @@
       <c r="R35" s="23"/>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A36" s="23"/>
-      <c r="B36" s="23"/>
-      <c r="C36" s="23"/>
-      <c r="D36" s="23"/>
-      <c r="E36" s="23"/>
-      <c r="F36" s="23"/>
-      <c r="G36" s="23"/>
+      <c r="A36" s="33" t="s">
+        <v>47</v>
+      </c>
+      <c r="B36" s="9"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="7"/>
       <c r="H36" s="23"/>
       <c r="I36" s="23"/>
       <c r="J36" s="23"/>
@@ -3850,13 +3896,13 @@
       <c r="R36" s="23"/>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A37" s="23"/>
-      <c r="B37" s="23"/>
-      <c r="C37" s="23"/>
-      <c r="D37" s="23"/>
-      <c r="E37" s="23"/>
-      <c r="F37" s="23"/>
-      <c r="G37" s="23"/>
+      <c r="A37" s="33"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="7"/>
       <c r="H37" s="23"/>
       <c r="I37" s="23"/>
       <c r="J37" s="23"/>
@@ -3870,13 +3916,13 @@
       <c r="R37" s="23"/>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A38" s="23"/>
-      <c r="B38" s="23"/>
-      <c r="C38" s="23"/>
-      <c r="D38" s="23"/>
-      <c r="E38" s="23"/>
-      <c r="F38" s="23"/>
-      <c r="G38" s="23"/>
+      <c r="A38" s="33"/>
+      <c r="B38" s="15"/>
+      <c r="C38" s="15"/>
+      <c r="D38" s="15"/>
+      <c r="E38" s="16"/>
+      <c r="F38" s="15"/>
+      <c r="G38" s="7"/>
       <c r="H38" s="23"/>
       <c r="I38" s="23"/>
       <c r="J38" s="23"/>
@@ -3890,13 +3936,12 @@
       <c r="R38" s="23"/>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A39" s="23"/>
-      <c r="B39" s="23"/>
-      <c r="C39" s="23"/>
-      <c r="D39" s="23"/>
-      <c r="E39" s="23"/>
-      <c r="F39" s="23"/>
-      <c r="G39" s="23"/>
+      <c r="A39" s="33"/>
+      <c r="B39" s="15"/>
+      <c r="C39" s="15"/>
+      <c r="D39" s="15"/>
+      <c r="E39" s="16"/>
+      <c r="F39" s="15"/>
       <c r="H39" s="23"/>
       <c r="I39" s="23"/>
       <c r="J39" s="23"/>
@@ -3910,13 +3955,12 @@
       <c r="R39" s="23"/>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A40" s="23"/>
-      <c r="B40" s="23"/>
-      <c r="C40" s="23"/>
-      <c r="D40" s="23"/>
-      <c r="E40" s="23"/>
-      <c r="F40" s="23"/>
-      <c r="G40" s="23"/>
+      <c r="A40" s="33"/>
+      <c r="B40" s="9"/>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="9"/>
       <c r="H40" s="23"/>
       <c r="I40" s="23"/>
       <c r="J40" s="23"/>
@@ -3930,13 +3974,12 @@
       <c r="R40" s="23"/>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A41" s="23"/>
-      <c r="B41" s="23"/>
-      <c r="C41" s="23"/>
-      <c r="D41" s="23"/>
-      <c r="E41" s="23"/>
-      <c r="F41" s="23"/>
-      <c r="G41" s="23"/>
+      <c r="A41" s="33"/>
+      <c r="B41" s="30"/>
+      <c r="C41" s="30"/>
+      <c r="D41" s="30"/>
+      <c r="E41" s="30"/>
+      <c r="F41" s="30"/>
       <c r="H41" s="23"/>
       <c r="I41" s="23"/>
       <c r="J41" s="23"/>
@@ -3950,13 +3993,14 @@
       <c r="R41" s="23"/>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A42" s="23"/>
-      <c r="B42" s="23"/>
-      <c r="C42" s="23"/>
-      <c r="D42" s="23"/>
-      <c r="E42" s="23"/>
-      <c r="F42" s="23"/>
-      <c r="G42" s="23"/>
+      <c r="A42" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="B42" s="15"/>
+      <c r="C42" s="15"/>
+      <c r="D42" s="15"/>
+      <c r="E42" s="16"/>
+      <c r="F42" s="15"/>
       <c r="H42" s="23"/>
       <c r="I42" s="23"/>
       <c r="J42" s="23"/>
@@ -4370,16 +4414,17 @@
       <c r="R62" s="23"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="A1:P3"/>
-    <mergeCell ref="A4:B5"/>
-    <mergeCell ref="C4:P5"/>
-    <mergeCell ref="A6:B20"/>
-    <mergeCell ref="C6:P7"/>
-    <mergeCell ref="C8:P9"/>
-    <mergeCell ref="C10:P11"/>
-    <mergeCell ref="C12:P13"/>
-    <mergeCell ref="C14:P15"/>
+  <mergeCells count="10">
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="A20:A24"/>
+    <mergeCell ref="A25:A35"/>
+    <mergeCell ref="A36:A41"/>
+    <mergeCell ref="A1:G3"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:F6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="A9:A12"/>
+    <mergeCell ref="A13:A16"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
